--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T08:42:11+00:00</t>
+    <t>2023-05-17T18:21:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:21:34+00:00</t>
+    <t>2023-05-17T18:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-17T18:27:08+00:00</t>
+    <t>2023-05-23T08:43:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-name.xlsx
+++ b/ig/mc-add-profils-dp/StructureDefinition-as-ext-practitionerrole-name.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-23T08:43:56+00:00</t>
+    <t>2023-05-23T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
